--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/206.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/206.xlsx
@@ -426,13 +426,13 @@
         <v>-3.177915252924698</v>
       </c>
       <c r="E2">
-        <v>-26.43586120586282</v>
+        <v>-19.50882206986776</v>
       </c>
       <c r="F2">
-        <v>-4.44660429751121</v>
+        <v>-4.720851893556043</v>
       </c>
       <c r="G2">
-        <v>-16.54947292548639</v>
+        <v>-11.96457757323754</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.211745234322818</v>
       </c>
       <c r="E3">
-        <v>-27.60615021519107</v>
+        <v>-20.44002576548704</v>
       </c>
       <c r="F3">
-        <v>-4.543764338552967</v>
+        <v>-4.325926905903976</v>
       </c>
       <c r="G3">
-        <v>-16.44007098232287</v>
+        <v>-11.95037533287407</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.137731081528943</v>
       </c>
       <c r="E4">
-        <v>-27.2765542914908</v>
+        <v>-21.66850113733984</v>
       </c>
       <c r="F4">
-        <v>-3.818845942117272</v>
+        <v>-4.630523398485173</v>
       </c>
       <c r="G4">
-        <v>-16.58387445945773</v>
+        <v>-11.77462840183078</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.935131011403462</v>
       </c>
       <c r="E5">
-        <v>-27.65708196235533</v>
+        <v>-21.53691273962496</v>
       </c>
       <c r="F5">
-        <v>-4.360670291512192</v>
+        <v>-4.111639855943382</v>
       </c>
       <c r="G5">
-        <v>-15.29150865765536</v>
+        <v>-11.16943088234216</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.605392045194149</v>
       </c>
       <c r="E6">
-        <v>-26.81149359632507</v>
+        <v>-21.3575217702851</v>
       </c>
       <c r="F6">
-        <v>-4.369214901272069</v>
+        <v>-4.293507090860611</v>
       </c>
       <c r="G6">
-        <v>-15.54219971861667</v>
+        <v>-11.58468254096956</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.154459315271225</v>
       </c>
       <c r="E7">
-        <v>-28.71259679795917</v>
+        <v>-22.20832240989819</v>
       </c>
       <c r="F7">
-        <v>-4.478607443750967</v>
+        <v>-4.605445403732821</v>
       </c>
       <c r="G7">
-        <v>-15.64953257081815</v>
+        <v>-10.79798767283593</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.5989751751463</v>
       </c>
       <c r="E8">
-        <v>-29.63880558674799</v>
+        <v>-22.86411790179298</v>
       </c>
       <c r="F8">
-        <v>-4.390382173515805</v>
+        <v>-4.275197686156534</v>
       </c>
       <c r="G8">
-        <v>-15.57086076662291</v>
+        <v>-9.789631917574857</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.9620525653979699</v>
       </c>
       <c r="E9">
-        <v>-29.9173542871968</v>
+        <v>-23.42618303867701</v>
       </c>
       <c r="F9">
-        <v>-4.407758008156928</v>
+        <v>-4.260089921464276</v>
       </c>
       <c r="G9">
-        <v>-15.52193090355248</v>
+        <v>-10.60478423516406</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.2674725826310878</v>
       </c>
       <c r="E10">
-        <v>-30.57343280871707</v>
+        <v>-23.83416684745006</v>
       </c>
       <c r="F10">
-        <v>-4.211855744334067</v>
+        <v>-4.296895113538061</v>
       </c>
       <c r="G10">
-        <v>-14.15949575013866</v>
+        <v>-9.828421579658498</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.4520047803142191</v>
       </c>
       <c r="E11">
-        <v>-29.23819866213344</v>
+        <v>-25.10618802536062</v>
       </c>
       <c r="F11">
-        <v>-4.541712472496233</v>
+        <v>-4.426893295161596</v>
       </c>
       <c r="G11">
-        <v>-15.61909872567563</v>
+        <v>-9.279407328516843</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.166951996667772</v>
       </c>
       <c r="E12">
-        <v>-30.68554423972497</v>
+        <v>-25.51648135587757</v>
       </c>
       <c r="F12">
-        <v>-4.549255586066125</v>
+        <v>-4.096626525135044</v>
       </c>
       <c r="G12">
-        <v>-12.96802378946388</v>
+        <v>-8.788499772680476</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.846301784680736</v>
       </c>
       <c r="E13">
-        <v>-31.83675025958489</v>
+        <v>-25.44432012256535</v>
       </c>
       <c r="F13">
-        <v>-3.977651428540562</v>
+        <v>-4.464506973820513</v>
       </c>
       <c r="G13">
-        <v>-12.97493620854988</v>
+        <v>-8.842123989325591</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>2.461539477096622</v>
       </c>
       <c r="E14">
-        <v>-32.27043995106247</v>
+        <v>-27.02042380161696</v>
       </c>
       <c r="F14">
-        <v>-4.201634518950923</v>
+        <v>-4.332775019222919</v>
       </c>
       <c r="G14">
-        <v>-13.69716647867005</v>
+        <v>-8.299820213992039</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.995490990866086</v>
       </c>
       <c r="E15">
-        <v>-32.10552198465113</v>
+        <v>-27.90899191445402</v>
       </c>
       <c r="F15">
-        <v>-3.930003735531535</v>
+        <v>-3.945427936571662</v>
       </c>
       <c r="G15">
-        <v>-12.11423740543138</v>
+        <v>-8.15041198325919</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.434764596688326</v>
       </c>
       <c r="E16">
-        <v>-32.35300535340732</v>
+        <v>-27.8766857808833</v>
       </c>
       <c r="F16">
-        <v>-3.903805788050598</v>
+        <v>-3.854372963288538</v>
       </c>
       <c r="G16">
-        <v>-13.19963948702791</v>
+        <v>-7.713446456439708</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.77948285502985</v>
       </c>
       <c r="E17">
-        <v>-34.08191785937376</v>
+        <v>-28.93459165076319</v>
       </c>
       <c r="F17">
-        <v>-3.909900087032994</v>
+        <v>-3.743131504766592</v>
       </c>
       <c r="G17">
-        <v>-11.33855010121582</v>
+        <v>-7.174360531370326</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.03457010806089</v>
       </c>
       <c r="E18">
-        <v>-34.33960161583223</v>
+        <v>-28.76201603480488</v>
       </c>
       <c r="F18">
-        <v>-3.803251925759572</v>
+        <v>-3.803367897195963</v>
       </c>
       <c r="G18">
-        <v>-12.17623399174531</v>
+        <v>-6.957691946916106</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.206435576010471</v>
       </c>
       <c r="E19">
-        <v>-35.82029714025324</v>
+        <v>-29.81038493842462</v>
       </c>
       <c r="F19">
-        <v>-3.439566329601879</v>
+        <v>-3.172431096077484</v>
       </c>
       <c r="G19">
-        <v>-11.90323647494039</v>
+        <v>-6.440495348952386</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.302978978293721</v>
       </c>
       <c r="E20">
-        <v>-34.71244899477976</v>
+        <v>-30.72889532140039</v>
       </c>
       <c r="F20">
-        <v>-3.260667963456284</v>
+        <v>-3.32395937486718</v>
       </c>
       <c r="G20">
-        <v>-11.54629345489617</v>
+        <v>-6.757993218896189</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.327007457018319</v>
       </c>
       <c r="E21">
-        <v>-35.95364711435711</v>
+        <v>-29.92032723038283</v>
       </c>
       <c r="F21">
-        <v>-3.256967646267979</v>
+        <v>-2.971626553964855</v>
       </c>
       <c r="G21">
-        <v>-11.6279315078946</v>
+        <v>-7.128314153464603</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.278034372719416</v>
       </c>
       <c r="E22">
-        <v>-37.00265453281192</v>
+        <v>-31.44200091609925</v>
       </c>
       <c r="F22">
-        <v>-3.679141779635136</v>
+        <v>-3.209561008173166</v>
       </c>
       <c r="G22">
-        <v>-12.08004609110179</v>
+        <v>-6.934319495408851</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.150674500899967</v>
       </c>
       <c r="E23">
-        <v>-37.62340642859836</v>
+        <v>-31.49802493228515</v>
       </c>
       <c r="F23">
-        <v>-3.358308457591665</v>
+        <v>-2.802901367893041</v>
       </c>
       <c r="G23">
-        <v>-11.12040170290555</v>
+        <v>-7.024925816273164</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.938174169279143</v>
       </c>
       <c r="E24">
-        <v>-36.83833658920661</v>
+        <v>-31.85692008281505</v>
       </c>
       <c r="F24">
-        <v>-3.150428829491726</v>
+        <v>-2.537441093257106</v>
       </c>
       <c r="G24">
-        <v>-10.55752619759097</v>
+        <v>-7.110996689748676</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.630783646067688</v>
       </c>
       <c r="E25">
-        <v>-37.02359193238639</v>
+        <v>-32.46443751331407</v>
       </c>
       <c r="F25">
-        <v>-2.897655001629665</v>
+        <v>-2.907167972883415</v>
       </c>
       <c r="G25">
-        <v>-11.70876509832698</v>
+        <v>-7.325496866874674</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.22541586325281</v>
       </c>
       <c r="E26">
-        <v>-37.06245982479422</v>
+        <v>-32.52788822687254</v>
       </c>
       <c r="F26">
-        <v>-3.168064771497328</v>
+        <v>-2.801389597382932</v>
       </c>
       <c r="G26">
-        <v>-11.18683442024211</v>
+        <v>-6.566835698367592</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.720974049093887</v>
       </c>
       <c r="E27">
-        <v>-37.12211341289726</v>
+        <v>-31.93251616366209</v>
       </c>
       <c r="F27">
-        <v>-3.11353748720805</v>
+        <v>-2.341518948616578</v>
       </c>
       <c r="G27">
-        <v>-11.68711744104569</v>
+        <v>-7.276517345621157</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.122883721177078</v>
       </c>
       <c r="E28">
-        <v>-38.089601506503</v>
+        <v>-32.48041396961312</v>
       </c>
       <c r="F28">
-        <v>-2.893512336248265</v>
+        <v>-2.719081355505967</v>
       </c>
       <c r="G28">
-        <v>-12.2397103919153</v>
+        <v>-7.210531551932403</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.447668005109475</v>
       </c>
       <c r="E29">
-        <v>-38.04595154554307</v>
+        <v>-32.14300642824962</v>
       </c>
       <c r="F29">
-        <v>-3.275807206109848</v>
+        <v>-2.502894030723352</v>
       </c>
       <c r="G29">
-        <v>-11.6648805066584</v>
+        <v>-7.360949499054729</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.7118583790036468</v>
       </c>
       <c r="E30">
-        <v>-37.58509553849347</v>
+        <v>-32.84098691976287</v>
       </c>
       <c r="F30">
-        <v>-3.227899405736341</v>
+        <v>-2.659718062319147</v>
       </c>
       <c r="G30">
-        <v>-12.15043159981223</v>
+        <v>-7.516075041933899</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.05601082974223544</v>
       </c>
       <c r="E31">
-        <v>-37.75581448010863</v>
+        <v>-31.97249806067581</v>
       </c>
       <c r="F31">
-        <v>-3.293472140974548</v>
+        <v>-2.708701083581487</v>
       </c>
       <c r="G31">
-        <v>-12.43806834899181</v>
+        <v>-7.472038165170513</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.8294832452152485</v>
       </c>
       <c r="E32">
-        <v>-37.4648532324048</v>
+        <v>-31.97710578297862</v>
       </c>
       <c r="F32">
-        <v>-3.108817449746899</v>
+        <v>-2.702644061132217</v>
       </c>
       <c r="G32">
-        <v>-11.51812071235697</v>
+        <v>-7.8444811594296</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.581901144321715</v>
       </c>
       <c r="E33">
-        <v>-36.7638907407575</v>
+        <v>-31.90414300976703</v>
       </c>
       <c r="F33">
-        <v>-3.369652949173004</v>
+        <v>-2.603463631995032</v>
       </c>
       <c r="G33">
-        <v>-12.45403842067325</v>
+        <v>-7.51365834369023</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.284131179013862</v>
       </c>
       <c r="E34">
-        <v>-36.59786329821429</v>
+        <v>-30.71146975341888</v>
       </c>
       <c r="F34">
-        <v>-3.027152020974506</v>
+        <v>-2.890191411330441</v>
       </c>
       <c r="G34">
-        <v>-11.32620176635434</v>
+        <v>-7.158297764413783</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.917591058125678</v>
       </c>
       <c r="E35">
-        <v>-36.00936772278449</v>
+        <v>-30.25914312716272</v>
       </c>
       <c r="F35">
-        <v>-2.949814811881742</v>
+        <v>-2.774258079839039</v>
       </c>
       <c r="G35">
-        <v>-11.11188366923301</v>
+        <v>-7.687912218695309</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.461920973576084</v>
       </c>
       <c r="E36">
-        <v>-35.41887509031731</v>
+        <v>-28.88668945271005</v>
       </c>
       <c r="F36">
-        <v>-3.156637443175708</v>
+        <v>-2.471813685770315</v>
       </c>
       <c r="G36">
-        <v>-11.51336676896258</v>
+        <v>-7.496519649433424</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.906267596587127</v>
       </c>
       <c r="E37">
-        <v>-34.72028551905004</v>
+        <v>-29.53932633398449</v>
       </c>
       <c r="F37">
-        <v>-3.335931768939842</v>
+        <v>-2.693923837482946</v>
       </c>
       <c r="G37">
-        <v>-11.81100798676183</v>
+        <v>-7.713731163356084</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.244997617257543</v>
       </c>
       <c r="E38">
-        <v>-34.76107122020012</v>
+        <v>-29.18526985793179</v>
       </c>
       <c r="F38">
-        <v>-2.807090421848998</v>
+        <v>-2.507131958356075</v>
       </c>
       <c r="G38">
-        <v>-12.01681798184724</v>
+        <v>-7.879112776315917</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.47565593516592</v>
       </c>
       <c r="E39">
-        <v>-33.67146603226654</v>
+        <v>-28.45278918719111</v>
       </c>
       <c r="F39">
-        <v>-3.389254607025449</v>
+        <v>-2.624307012584273</v>
       </c>
       <c r="G39">
-        <v>-12.72251704281707</v>
+        <v>-8.039482223329291</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.606837477160643</v>
       </c>
       <c r="E40">
-        <v>-33.18004961837617</v>
+        <v>-27.68454715721186</v>
       </c>
       <c r="F40">
-        <v>-3.016608560671674</v>
+        <v>-3.000723787355591</v>
       </c>
       <c r="G40">
-        <v>-12.41865199940398</v>
+        <v>-8.041342749922361</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.646894953206119</v>
       </c>
       <c r="E41">
-        <v>-32.83683883757184</v>
+        <v>-27.32747698170705</v>
       </c>
       <c r="F41">
-        <v>-3.154823318563577</v>
+        <v>-2.542620874626811</v>
       </c>
       <c r="G41">
-        <v>-12.54510490736752</v>
+        <v>-7.626064606930645</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.614105917668692</v>
       </c>
       <c r="E42">
-        <v>-31.6379774214922</v>
+        <v>-27.55986921083268</v>
       </c>
       <c r="F42">
-        <v>-2.457517721132801</v>
+        <v>-2.341378954525505</v>
       </c>
       <c r="G42">
-        <v>-11.83313236260078</v>
+        <v>-8.429871684956767</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.525925224966658</v>
       </c>
       <c r="E43">
-        <v>-32.05890134474217</v>
+        <v>-26.18305461591062</v>
       </c>
       <c r="F43">
-        <v>-2.803737190602466</v>
+        <v>-2.461266911997872</v>
       </c>
       <c r="G43">
-        <v>-13.82766652855535</v>
+        <v>-7.772794606322222</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.401945115248719</v>
       </c>
       <c r="E44">
-        <v>-32.42112718790471</v>
+        <v>-26.33381657257398</v>
       </c>
       <c r="F44">
-        <v>-3.001994502951485</v>
+        <v>-2.410076291607071</v>
       </c>
       <c r="G44">
-        <v>-12.38993632739634</v>
+        <v>-8.179687137462965</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.263640903372456</v>
       </c>
       <c r="E45">
-        <v>-30.09063860933731</v>
+        <v>-26.11789440341425</v>
       </c>
       <c r="F45">
-        <v>-2.460451798473517</v>
+        <v>-2.47249874561243</v>
       </c>
       <c r="G45">
-        <v>-13.59448659822401</v>
+        <v>-7.849791274474591</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.123397211644133</v>
       </c>
       <c r="E46">
-        <v>-31.20030493712487</v>
+        <v>-24.92667478722256</v>
       </c>
       <c r="F46">
-        <v>-2.574436809833534</v>
+        <v>-2.284224088834547</v>
       </c>
       <c r="G46">
-        <v>-12.47815905547238</v>
+        <v>-8.491560390535547</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.998628543663605</v>
       </c>
       <c r="E47">
-        <v>-30.94680096217548</v>
+        <v>-24.48677429364345</v>
       </c>
       <c r="F47">
-        <v>-2.604885110458236</v>
+        <v>-2.42850746631936</v>
       </c>
       <c r="G47">
-        <v>-12.53819248828152</v>
+        <v>-8.205880173769678</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.895279426985114</v>
       </c>
       <c r="E48">
-        <v>-30.47847976572424</v>
+        <v>-23.33079526217945</v>
       </c>
       <c r="F48">
-        <v>-2.582706401615682</v>
+        <v>-2.428622609388349</v>
       </c>
       <c r="G48">
-        <v>-12.63235764560056</v>
+        <v>-8.237267456027508</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.818870007688811</v>
       </c>
       <c r="E49">
-        <v>-29.83254955445516</v>
+        <v>-23.60373997604376</v>
       </c>
       <c r="F49">
-        <v>-2.545801805453561</v>
+        <v>-2.080467245298342</v>
       </c>
       <c r="G49">
-        <v>-13.77560157885923</v>
+        <v>-8.409227122973872</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.772700731684422</v>
       </c>
       <c r="E50">
-        <v>-28.87158699189447</v>
+        <v>-23.14254659768059</v>
       </c>
       <c r="F50">
-        <v>-2.554168316221836</v>
+        <v>-2.185080936230488</v>
       </c>
       <c r="G50">
-        <v>-13.02936488776103</v>
+        <v>-9.030669489423703</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.749819212299965</v>
       </c>
       <c r="E51">
-        <v>-28.16884480996216</v>
+        <v>-22.02786272069253</v>
       </c>
       <c r="F51">
-        <v>-2.50374559241343</v>
+        <v>-2.130334134579469</v>
       </c>
       <c r="G51">
-        <v>-13.66929996159323</v>
+        <v>-9.083088667492522</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.751369533910419</v>
       </c>
       <c r="E52">
-        <v>-27.98026556686075</v>
+        <v>-21.29600697936491</v>
       </c>
       <c r="F52">
-        <v>-2.091665944216788</v>
+        <v>-2.118590369909981</v>
       </c>
       <c r="G52">
-        <v>-12.97378082815667</v>
+        <v>-9.067366886726523</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.768402571005054</v>
       </c>
       <c r="E53">
-        <v>-27.42736153289423</v>
+        <v>-21.55705086353706</v>
       </c>
       <c r="F53">
-        <v>-2.584411181730643</v>
+        <v>-2.61445275396057</v>
       </c>
       <c r="G53">
-        <v>-13.48852431187579</v>
+        <v>-9.210170579108524</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.7949710626684</v>
       </c>
       <c r="E54">
-        <v>-27.45907896484396</v>
+        <v>-20.42739585147965</v>
       </c>
       <c r="F54">
-        <v>-2.680095072060611</v>
+        <v>-2.106914531367522</v>
       </c>
       <c r="G54">
-        <v>-14.03353611346047</v>
+        <v>-8.950941621201434</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.827191925353654</v>
       </c>
       <c r="E55">
-        <v>-26.1182747952309</v>
+        <v>-21.47383562517211</v>
       </c>
       <c r="F55">
-        <v>-2.506692923632591</v>
+        <v>-2.167183230125602</v>
       </c>
       <c r="G55">
-        <v>-13.68806578898259</v>
+        <v>-8.660335312673132</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.854335433295286</v>
       </c>
       <c r="E56">
-        <v>-27.24270847675747</v>
+        <v>-20.49371535332198</v>
       </c>
       <c r="F56">
-        <v>-2.384792861738824</v>
+        <v>-2.017144355926139</v>
       </c>
       <c r="G56">
-        <v>-13.64831606869256</v>
+        <v>-9.239902588596721</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.876474935010817</v>
       </c>
       <c r="E57">
-        <v>-26.35682122053295</v>
+        <v>-19.96328160738153</v>
       </c>
       <c r="F57">
-        <v>-2.372967917063861</v>
+        <v>-1.884179790633179</v>
       </c>
       <c r="G57">
-        <v>-12.92446694180369</v>
+        <v>-10.15570542221639</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.8875869165246</v>
       </c>
       <c r="E58">
-        <v>-25.16231393221168</v>
+        <v>-20.09406846519706</v>
       </c>
       <c r="F58">
-        <v>-2.587378393767471</v>
+        <v>-2.015177811711893</v>
       </c>
       <c r="G58">
-        <v>-14.167174560517</v>
+        <v>-9.590383423748282</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.884664288300373</v>
       </c>
       <c r="E59">
-        <v>-25.90046878088397</v>
+        <v>-19.70980480327619</v>
       </c>
       <c r="F59">
-        <v>-2.643425732240886</v>
+        <v>-2.185278916039758</v>
       </c>
       <c r="G59">
-        <v>-14.19314910081812</v>
+        <v>-9.708659284229823</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.867229424008507</v>
       </c>
       <c r="E60">
-        <v>-26.50394681256815</v>
+        <v>-19.20670492644603</v>
       </c>
       <c r="F60">
-        <v>-2.864275108766456</v>
+        <v>-2.346267150569425</v>
       </c>
       <c r="G60">
-        <v>-14.57597562116113</v>
+        <v>-9.602751621883</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.828597329228421</v>
       </c>
       <c r="E61">
-        <v>-25.30837080438107</v>
+        <v>-19.00943101324989</v>
       </c>
       <c r="F61">
-        <v>-2.70587635073794</v>
+        <v>-2.392380707148468</v>
       </c>
       <c r="G61">
-        <v>-14.62234312198416</v>
+        <v>-9.6220057547394</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.769936383340216</v>
       </c>
       <c r="E62">
-        <v>-23.81069123819429</v>
+        <v>-18.75889318877553</v>
       </c>
       <c r="F62">
-        <v>-2.472719091341575</v>
+        <v>-2.508203037407895</v>
       </c>
       <c r="G62">
-        <v>-13.87488980540028</v>
+        <v>-9.950858795882903</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.686224619953826</v>
       </c>
       <c r="E63">
-        <v>-24.02051355286569</v>
+        <v>-18.4168666039242</v>
       </c>
       <c r="F63">
-        <v>-3.181162916870393</v>
+        <v>-2.406441415443586</v>
       </c>
       <c r="G63">
-        <v>-14.2537420158234</v>
+        <v>-9.818797823775837</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.574639306007015</v>
       </c>
       <c r="E64">
-        <v>-23.91160828145523</v>
+        <v>-18.36717565863804</v>
       </c>
       <c r="F64">
-        <v>-2.746436532248616</v>
+        <v>-2.231590452428069</v>
       </c>
       <c r="G64">
-        <v>-14.98220604319402</v>
+        <v>-10.15982374086724</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.434128417376844</v>
       </c>
       <c r="E65">
-        <v>-24.20243593917584</v>
+        <v>-17.64301832312345</v>
       </c>
       <c r="F65">
-        <v>-2.895132622888141</v>
+        <v>-2.302869810704161</v>
       </c>
       <c r="G65">
-        <v>-14.50561990736054</v>
+        <v>-10.23074886850059</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.25962569696608</v>
       </c>
       <c r="E66">
-        <v>-24.13575415941289</v>
+        <v>-17.16983354558797</v>
       </c>
       <c r="F66">
-        <v>-2.51232665033903</v>
+        <v>-2.457800194417155</v>
       </c>
       <c r="G66">
-        <v>-14.79808012139083</v>
+        <v>-10.27540812782535</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.053594584039118</v>
       </c>
       <c r="E67">
-        <v>-24.27288088083915</v>
+        <v>-18.03709518821894</v>
       </c>
       <c r="F67">
-        <v>-2.843184046323778</v>
+        <v>-2.395265082445015</v>
       </c>
       <c r="G67">
-        <v>-14.56139101278787</v>
+        <v>-10.70256119766644</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.81407691080698</v>
       </c>
       <c r="E68">
-        <v>-24.00668812172028</v>
+        <v>-16.76574422446152</v>
       </c>
       <c r="F68">
-        <v>-2.994022295066943</v>
+        <v>-2.311715946198657</v>
       </c>
       <c r="G68">
-        <v>-14.84910721506039</v>
+        <v>-11.10559363270839</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.543960754622856</v>
       </c>
       <c r="E69">
-        <v>-23.4757109588989</v>
+        <v>-17.56207185023635</v>
       </c>
       <c r="F69">
-        <v>-2.76408821323487</v>
+        <v>-2.677938831711124</v>
       </c>
       <c r="G69">
-        <v>-14.22509917581762</v>
+        <v>-10.32145450573108</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.246595631891022</v>
       </c>
       <c r="E70">
-        <v>-24.23630892475321</v>
+        <v>-16.62082852774206</v>
       </c>
       <c r="F70">
-        <v>-3.190235196665853</v>
+        <v>-2.442999754031337</v>
       </c>
       <c r="G70">
-        <v>-14.60285725094001</v>
+        <v>-9.856773091656816</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.923423572923836</v>
       </c>
       <c r="E71">
-        <v>-24.26328957289091</v>
+        <v>-17.28135174650086</v>
       </c>
       <c r="F71">
-        <v>-2.826594332347912</v>
+        <v>-2.790577746041593</v>
       </c>
       <c r="G71">
-        <v>-14.2205488309739</v>
+        <v>-10.47328274525313</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.581652658784637</v>
       </c>
       <c r="E72">
-        <v>-23.61479398109648</v>
+        <v>-17.04941689325001</v>
       </c>
       <c r="F72">
-        <v>-3.025764505574817</v>
+        <v>-2.614178564350244</v>
       </c>
       <c r="G72">
-        <v>-14.15791496464366</v>
+        <v>-10.4898619573138</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.223690698694659</v>
       </c>
       <c r="E73">
-        <v>-24.96157573639967</v>
+        <v>-17.64362966711449</v>
       </c>
       <c r="F73">
-        <v>-3.12382581035082</v>
+        <v>-2.906950112256478</v>
       </c>
       <c r="G73">
-        <v>-13.93757167464084</v>
+        <v>-10.43950524911595</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.8565597636555249</v>
       </c>
       <c r="E74">
-        <v>-24.50883701900882</v>
+        <v>-18.12081761567275</v>
       </c>
       <c r="F74">
-        <v>-3.46155451394179</v>
+        <v>-2.723061660876419</v>
       </c>
       <c r="G74">
-        <v>-14.08944129598214</v>
+        <v>-10.52898929504245</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.4858578646470937</v>
       </c>
       <c r="E75">
-        <v>-25.63106080521965</v>
+        <v>-18.36528728497684</v>
       </c>
       <c r="F75">
-        <v>-3.065806957458742</v>
+        <v>-2.903363281402357</v>
       </c>
       <c r="G75">
-        <v>-13.71072978374444</v>
+        <v>-10.55432158950895</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.1159133532031444</v>
       </c>
       <c r="E76">
-        <v>-25.93866645913867</v>
+        <v>-18.50425709532422</v>
       </c>
       <c r="F76">
-        <v>-2.971053323722118</v>
+        <v>-2.786230473911701</v>
       </c>
       <c r="G76">
-        <v>-13.70353265774207</v>
+        <v>-9.773751230622974</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.2452077445759208</v>
       </c>
       <c r="E77">
-        <v>-24.45782828778642</v>
+        <v>-19.65489252745918</v>
       </c>
       <c r="F77">
-        <v>-3.082982327188387</v>
+        <v>-3.032157016822221</v>
       </c>
       <c r="G77">
-        <v>-13.35564563502052</v>
+        <v>-10.00425789543135</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.5942201410405096</v>
       </c>
       <c r="E78">
-        <v>-24.57585843432234</v>
+        <v>-19.05456178521034</v>
       </c>
       <c r="F78">
-        <v>-3.313294144556137</v>
+        <v>-3.182180980408434</v>
       </c>
       <c r="G78">
-        <v>-13.70379419083967</v>
+        <v>-9.865807570433487</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.9240812460498312</v>
       </c>
       <c r="E79">
-        <v>-26.16864501161821</v>
+        <v>-18.33536312873415</v>
       </c>
       <c r="F79">
-        <v>-3.306828736977287</v>
+        <v>-3.017371487049652</v>
       </c>
       <c r="G79">
-        <v>-12.93763960250445</v>
+        <v>-9.679046454381043</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.229140923128634</v>
       </c>
       <c r="E80">
-        <v>-26.05178773985028</v>
+        <v>-20.93166860307779</v>
       </c>
       <c r="F80">
-        <v>-3.472188266291527</v>
+        <v>-3.13531857969726</v>
       </c>
       <c r="G80">
-        <v>-13.72553288812329</v>
+        <v>-10.16855033890876</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.504371073589441</v>
       </c>
       <c r="E81">
-        <v>-26.24139494655144</v>
+        <v>-20.29213938981855</v>
       </c>
       <c r="F81">
-        <v>-3.334575731501459</v>
+        <v>-3.172086495237919</v>
       </c>
       <c r="G81">
-        <v>-13.85505467180174</v>
+        <v>-9.157072739204155</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.7421839321052</v>
       </c>
       <c r="E82">
-        <v>-28.24253666748898</v>
+        <v>-20.8507357156127</v>
       </c>
       <c r="F82">
-        <v>-3.408879459165172</v>
+        <v>-3.382467792894312</v>
       </c>
       <c r="G82">
-        <v>-13.03935611419855</v>
+        <v>-8.779193829169584</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.937910205348334</v>
       </c>
       <c r="E83">
-        <v>-27.14641047698436</v>
+        <v>-21.3945963869859</v>
       </c>
       <c r="F83">
-        <v>-3.681992191868169</v>
+        <v>-3.001213352490645</v>
       </c>
       <c r="G83">
-        <v>-11.94242671303428</v>
+        <v>-9.30858316635444</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.085045582836563</v>
       </c>
       <c r="E84">
-        <v>-28.66761093716698</v>
+        <v>-22.70712476489507</v>
       </c>
       <c r="F84">
-        <v>-3.968210525250857</v>
+        <v>-3.071669313568354</v>
       </c>
       <c r="G84">
-        <v>-12.82590538000851</v>
+        <v>-8.994240246309563</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.178343327440892</v>
       </c>
       <c r="E85">
-        <v>-29.94331602868277</v>
+        <v>-23.11178014527248</v>
       </c>
       <c r="F85">
-        <v>-3.677922422818215</v>
+        <v>-3.077616163153052</v>
       </c>
       <c r="G85">
-        <v>-12.19058189611251</v>
+        <v>-8.277066834500626</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.213626512444818</v>
       </c>
       <c r="E86">
-        <v>-31.3303853529952</v>
+        <v>-24.24603155844768</v>
       </c>
       <c r="F86">
-        <v>-4.09032844777156</v>
+        <v>-3.518465011248921</v>
       </c>
       <c r="G86">
-        <v>-11.74857771898226</v>
+        <v>-8.762124656369101</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.188065062913495</v>
       </c>
       <c r="E87">
-        <v>-30.85055051137945</v>
+        <v>-24.93996132996106</v>
       </c>
       <c r="F87">
-        <v>-4.250379798768661</v>
+        <v>-3.385373705743333</v>
       </c>
       <c r="G87">
-        <v>-13.5317368627999</v>
+        <v>-8.002082990372145</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.100692989998465</v>
       </c>
       <c r="E88">
-        <v>-31.69705589339627</v>
+        <v>-25.81646105956768</v>
       </c>
       <c r="F88">
-        <v>-4.199600048609648</v>
+        <v>-3.753770227320746</v>
       </c>
       <c r="G88">
-        <v>-12.01460653742701</v>
+        <v>-8.87901339826969</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.953950866245105</v>
       </c>
       <c r="E89">
-        <v>-33.63870478705805</v>
+        <v>-27.46670491507287</v>
       </c>
       <c r="F89">
-        <v>-4.042621112309531</v>
+        <v>-3.864567680914791</v>
       </c>
       <c r="G89">
-        <v>-12.69250363695803</v>
+        <v>-8.230139851481457</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.751327141860727</v>
       </c>
       <c r="E90">
-        <v>-34.61385053021075</v>
+        <v>-28.90911445599604</v>
       </c>
       <c r="F90">
-        <v>-4.569679812749549</v>
+        <v>-4.12965022001505</v>
       </c>
       <c r="G90">
-        <v>-11.92508607549958</v>
+        <v>-8.521120251655699</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.498066677330247</v>
       </c>
       <c r="E91">
-        <v>-36.42592846132806</v>
+        <v>-30.16641809338167</v>
       </c>
       <c r="F91">
-        <v>-4.229403051027568</v>
+        <v>-4.104478619746181</v>
       </c>
       <c r="G91">
-        <v>-11.82716344899348</v>
+        <v>-7.726215230584677</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.202806578791101</v>
       </c>
       <c r="E92">
-        <v>-36.77554929709025</v>
+        <v>-31.40166353387593</v>
       </c>
       <c r="F92">
-        <v>-3.991837220313504</v>
+        <v>-4.038213369359235</v>
       </c>
       <c r="G92">
-        <v>-11.473865339588</v>
+        <v>-8.632626046509431</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.8712242657209086</v>
       </c>
       <c r="E93">
-        <v>-37.92867538992942</v>
+        <v>-33.63290607609122</v>
       </c>
       <c r="F93">
-        <v>-4.582068047258416</v>
+        <v>-4.728115018943789</v>
       </c>
       <c r="G93">
-        <v>-12.25800777711085</v>
+        <v>-8.474448180643053</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.5123395592926554</v>
       </c>
       <c r="E94">
-        <v>-39.86789022881208</v>
+        <v>-34.36341006792755</v>
       </c>
       <c r="F94">
-        <v>-4.94486066335589</v>
+        <v>-4.531827564278626</v>
       </c>
       <c r="G94">
-        <v>-12.73860960468346</v>
+        <v>-8.147465597729239</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.1334114745280182</v>
       </c>
       <c r="E95">
-        <v>-40.63106716061375</v>
+        <v>-35.88828991324141</v>
       </c>
       <c r="F95">
-        <v>-4.635606260868751</v>
+        <v>-4.789720702689988</v>
       </c>
       <c r="G95">
-        <v>-12.79041302128198</v>
+        <v>-8.46669819353562</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.2630314500662621</v>
       </c>
       <c r="E96">
-        <v>-42.84135192512154</v>
+        <v>-38.59328329224314</v>
       </c>
       <c r="F96">
-        <v>-5.197014872400657</v>
+        <v>-5.047598102120697</v>
       </c>
       <c r="G96">
-        <v>-13.20584675991404</v>
+        <v>-8.59733894160634</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.6648540583868299</v>
       </c>
       <c r="E97">
-        <v>-43.30410989125437</v>
+        <v>-40.48750094914858</v>
       </c>
       <c r="F97">
-        <v>-5.22397491789217</v>
+        <v>-5.324162641791159</v>
       </c>
       <c r="G97">
-        <v>-13.32146756287309</v>
+        <v>-9.269008904977992</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.077924278365094</v>
       </c>
       <c r="E98">
-        <v>-45.88436645371483</v>
+        <v>-42.17572964463011</v>
       </c>
       <c r="F98">
-        <v>-5.091455185894514</v>
+        <v>-5.421560424277519</v>
       </c>
       <c r="G98">
-        <v>-13.21231887644332</v>
+        <v>-8.94296982754287</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.483921347964782</v>
       </c>
       <c r="E99">
-        <v>-46.75831212398112</v>
+        <v>-43.50401031937496</v>
       </c>
       <c r="F99">
-        <v>-5.501690059885121</v>
+        <v>-5.398565773543208</v>
       </c>
       <c r="G99">
-        <v>-13.33209441405415</v>
+        <v>-9.124318201638605</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.900715382002155</v>
       </c>
       <c r="E100">
-        <v>-48.12864420836119</v>
+        <v>-46.13499484766934</v>
       </c>
       <c r="F100">
-        <v>-5.533534987950943</v>
+        <v>-5.715930721271157</v>
       </c>
       <c r="G100">
-        <v>-13.84622048103019</v>
+        <v>-9.595322757692875</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.293254873064213</v>
       </c>
       <c r="E101">
-        <v>-50.81526670043231</v>
+        <v>-48.02333228107582</v>
       </c>
       <c r="F101">
-        <v>-6.011592443045759</v>
+        <v>-6.063209672649002</v>
       </c>
       <c r="G101">
-        <v>-13.21200768516263</v>
+        <v>-9.851545740250307</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.713406755778496</v>
       </c>
       <c r="E102">
-        <v>-52.20282509993757</v>
+        <v>-50.76053556357561</v>
       </c>
       <c r="F102">
-        <v>-5.904248453153985</v>
+        <v>-6.357270988601396</v>
       </c>
       <c r="G102">
-        <v>-14.90301448334911</v>
+        <v>-10.61295135100944</v>
       </c>
     </row>
   </sheetData>
